--- a/Team-Data/2007-08/12-9-2007-08.xlsx
+++ b/Team-Data/2007-08/12-9-2007-08.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -739,16 +806,16 @@
         <v>-1.3</v>
       </c>
       <c r="AD2" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="AE2" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AF2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AG2" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AH2" t="n">
         <v>2</v>
@@ -772,22 +839,22 @@
         <v>30</v>
       </c>
       <c r="AO2" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AP2" t="n">
         <v>11</v>
       </c>
       <c r="AQ2" t="n">
+        <v>11</v>
+      </c>
+      <c r="AR2" t="n">
         <v>12</v>
       </c>
-      <c r="AR2" t="n">
-        <v>13</v>
-      </c>
       <c r="AS2" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AT2" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AU2" t="n">
         <v>24</v>
@@ -796,22 +863,22 @@
         <v>19</v>
       </c>
       <c r="AW2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AX2" t="n">
         <v>2</v>
       </c>
       <c r="AY2" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AZ2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BA2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BB2" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BC2" t="n">
         <v>17</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>12-9-2007-08</t>
+          <t>2007-12-09</t>
         </is>
       </c>
     </row>
@@ -921,7 +988,7 @@
         <v>13.9</v>
       </c>
       <c r="AD3" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="AE3" t="n">
         <v>1</v>
@@ -945,19 +1012,19 @@
         <v>3</v>
       </c>
       <c r="AL3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AM3" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AN3" t="n">
         <v>4</v>
       </c>
       <c r="AO3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AP3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AQ3" t="n">
         <v>10</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>12-9-2007-08</t>
+          <t>2007-12-09</t>
         </is>
       </c>
     </row>
@@ -1025,16 +1092,16 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E4" t="n">
         <v>7</v>
       </c>
       <c r="F4" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G4" t="n">
-        <v>0.368</v>
+        <v>0.389</v>
       </c>
       <c r="H4" t="n">
         <v>48.3</v>
@@ -1046,76 +1113,76 @@
         <v>78.3</v>
       </c>
       <c r="K4" t="n">
-        <v>0.431</v>
+        <v>0.432</v>
       </c>
       <c r="L4" t="n">
         <v>6.3</v>
       </c>
       <c r="M4" t="n">
-        <v>17.4</v>
+        <v>17.3</v>
       </c>
       <c r="N4" t="n">
-        <v>0.36</v>
+        <v>0.363</v>
       </c>
       <c r="O4" t="n">
-        <v>17.8</v>
+        <v>18.2</v>
       </c>
       <c r="P4" t="n">
-        <v>25.9</v>
+        <v>26.6</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.6879999999999999</v>
+        <v>0.6850000000000001</v>
       </c>
       <c r="R4" t="n">
-        <v>12.2</v>
+        <v>12.4</v>
       </c>
       <c r="S4" t="n">
-        <v>27.8</v>
+        <v>28.2</v>
       </c>
       <c r="T4" t="n">
-        <v>40</v>
+        <v>40.6</v>
       </c>
       <c r="U4" t="n">
-        <v>19.1</v>
+        <v>18.9</v>
       </c>
       <c r="V4" t="n">
-        <v>16.5</v>
+        <v>16.8</v>
       </c>
       <c r="W4" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="X4" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="Y4" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="Z4" t="n">
-        <v>23.5</v>
+        <v>23.3</v>
       </c>
       <c r="AA4" t="n">
-        <v>21.3</v>
+        <v>21.6</v>
       </c>
       <c r="AB4" t="n">
-        <v>91.7</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="AC4" t="n">
-        <v>-6.2</v>
+        <v>-5.4</v>
       </c>
       <c r="AD4" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="AE4" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AF4" t="n">
         <v>18</v>
       </c>
       <c r="AG4" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AH4" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AI4" t="n">
         <v>27</v>
@@ -1124,7 +1191,7 @@
         <v>25</v>
       </c>
       <c r="AK4" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AL4" t="n">
         <v>13</v>
@@ -1133,49 +1200,49 @@
         <v>15</v>
       </c>
       <c r="AN4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AO4" t="n">
         <v>18</v>
       </c>
       <c r="AP4" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AQ4" t="n">
         <v>29</v>
       </c>
       <c r="AR4" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AS4" t="n">
         <v>30</v>
       </c>
       <c r="AT4" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AU4" t="n">
         <v>26</v>
       </c>
       <c r="AV4" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AW4" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AX4" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AY4" t="n">
         <v>30</v>
       </c>
       <c r="AZ4" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BA4" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="BB4" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BC4" t="n">
         <v>26</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>12-9-2007-08</t>
+          <t>2007-12-09</t>
         </is>
       </c>
     </row>
@@ -1285,13 +1352,13 @@
         <v>-5.1</v>
       </c>
       <c r="AD5" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="AE5" t="n">
         <v>25</v>
       </c>
       <c r="AF5" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="AG5" t="n">
         <v>25</v>
@@ -1324,7 +1391,7 @@
         <v>24</v>
       </c>
       <c r="AQ5" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AR5" t="n">
         <v>1</v>
@@ -1333,10 +1400,10 @@
         <v>21</v>
       </c>
       <c r="AT5" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AU5" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AV5" t="n">
         <v>14</v>
@@ -1345,7 +1412,7 @@
         <v>12</v>
       </c>
       <c r="AX5" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AY5" t="n">
         <v>29</v>
@@ -1360,7 +1427,7 @@
         <v>30</v>
       </c>
       <c r="BC5" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="BD5" t="n">
         <v>10</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>12-9-2007-08</t>
+          <t>2007-12-09</t>
         </is>
       </c>
     </row>
@@ -1470,19 +1537,19 @@
         <v>1</v>
       </c>
       <c r="AE6" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AF6" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="AG6" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AH6" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AI6" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AJ6" t="n">
         <v>12</v>
@@ -1491,25 +1558,25 @@
         <v>24</v>
       </c>
       <c r="AL6" t="n">
+        <v>10</v>
+      </c>
+      <c r="AM6" t="n">
         <v>9</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>8</v>
       </c>
       <c r="AN6" t="n">
         <v>7</v>
       </c>
       <c r="AO6" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AP6" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AQ6" t="n">
         <v>26</v>
       </c>
       <c r="AR6" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AS6" t="n">
         <v>14</v>
@@ -1524,25 +1591,25 @@
         <v>18</v>
       </c>
       <c r="AW6" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AX6" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AY6" t="n">
         <v>21</v>
       </c>
       <c r="AZ6" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="BA6" t="n">
         <v>28</v>
       </c>
       <c r="BB6" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BC6" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="BD6" t="n">
         <v>10</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>12-9-2007-08</t>
+          <t>2007-12-09</t>
         </is>
       </c>
     </row>
@@ -1652,7 +1719,7 @@
         <v>1</v>
       </c>
       <c r="AE7" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AF7" t="n">
         <v>7</v>
@@ -1661,7 +1728,7 @@
         <v>7</v>
       </c>
       <c r="AH7" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AI7" t="n">
         <v>14</v>
@@ -1679,28 +1746,28 @@
         <v>17</v>
       </c>
       <c r="AN7" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AO7" t="n">
         <v>1</v>
       </c>
       <c r="AP7" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AQ7" t="n">
         <v>1</v>
       </c>
       <c r="AR7" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AS7" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AT7" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AU7" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AV7" t="n">
         <v>4</v>
@@ -1709,10 +1776,10 @@
         <v>29</v>
       </c>
       <c r="AX7" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AY7" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AZ7" t="n">
         <v>23</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>12-9-2007-08</t>
+          <t>2007-12-09</t>
         </is>
       </c>
     </row>
@@ -1834,7 +1901,7 @@
         <v>1</v>
       </c>
       <c r="AE8" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AF8" t="n">
         <v>7</v>
@@ -1843,7 +1910,7 @@
         <v>7</v>
       </c>
       <c r="AH8" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AI8" t="n">
         <v>4</v>
@@ -1852,7 +1919,7 @@
         <v>6</v>
       </c>
       <c r="AK8" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AL8" t="n">
         <v>12</v>
@@ -1861,7 +1928,7 @@
         <v>13</v>
       </c>
       <c r="AN8" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AO8" t="n">
         <v>3</v>
@@ -1870,7 +1937,7 @@
         <v>1</v>
       </c>
       <c r="AQ8" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AR8" t="n">
         <v>17</v>
@@ -1879,7 +1946,7 @@
         <v>6</v>
       </c>
       <c r="AT8" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AU8" t="n">
         <v>4</v>
@@ -1894,7 +1961,7 @@
         <v>1</v>
       </c>
       <c r="AY8" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AZ8" t="n">
         <v>18</v>
@@ -1903,7 +1970,7 @@
         <v>2</v>
       </c>
       <c r="BB8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BC8" t="n">
         <v>7</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>12-9-2007-08</t>
+          <t>2007-12-09</t>
         </is>
       </c>
     </row>
@@ -1935,25 +2002,25 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E9" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F9" t="n">
         <v>6</v>
       </c>
       <c r="G9" t="n">
-        <v>0.7</v>
+        <v>0.6840000000000001</v>
       </c>
       <c r="H9" t="n">
         <v>48</v>
       </c>
       <c r="I9" t="n">
-        <v>37.7</v>
+        <v>37.9</v>
       </c>
       <c r="J9" t="n">
-        <v>80.09999999999999</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="K9" t="n">
         <v>0.471</v>
@@ -1962,34 +2029,34 @@
         <v>5.7</v>
       </c>
       <c r="M9" t="n">
-        <v>16.2</v>
+        <v>15.9</v>
       </c>
       <c r="N9" t="n">
-        <v>0.353</v>
+        <v>0.358</v>
       </c>
       <c r="O9" t="n">
-        <v>19.1</v>
+        <v>18.4</v>
       </c>
       <c r="P9" t="n">
-        <v>25.4</v>
+        <v>24.8</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.751</v>
+        <v>0.741</v>
       </c>
       <c r="R9" t="n">
-        <v>12.1</v>
+        <v>12</v>
       </c>
       <c r="S9" t="n">
-        <v>29.3</v>
+        <v>29</v>
       </c>
       <c r="T9" t="n">
-        <v>41.3</v>
+        <v>41</v>
       </c>
       <c r="U9" t="n">
-        <v>23.9</v>
+        <v>24.1</v>
       </c>
       <c r="V9" t="n">
-        <v>12</v>
+        <v>11.7</v>
       </c>
       <c r="W9" t="n">
         <v>6.6</v>
@@ -2001,19 +2068,19 @@
         <v>3.4</v>
       </c>
       <c r="Z9" t="n">
-        <v>20.2</v>
+        <v>20.4</v>
       </c>
       <c r="AA9" t="n">
-        <v>20.8</v>
+        <v>20.5</v>
       </c>
       <c r="AB9" t="n">
-        <v>100.2</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="AC9" t="n">
-        <v>8.300000000000001</v>
+        <v>7.7</v>
       </c>
       <c r="AD9" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="AE9" t="n">
         <v>5</v>
@@ -2025,43 +2092,43 @@
         <v>5</v>
       </c>
       <c r="AH9" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AI9" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AJ9" t="n">
+        <v>14</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>5</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>19</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>22</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>12</v>
+      </c>
+      <c r="AO9" t="n">
         <v>17</v>
       </c>
-      <c r="AK9" t="n">
-        <v>6</v>
-      </c>
-      <c r="AL9" t="n">
+      <c r="AP9" t="n">
         <v>20</v>
       </c>
-      <c r="AM9" t="n">
-        <v>21</v>
-      </c>
-      <c r="AN9" t="n">
-        <v>15</v>
-      </c>
-      <c r="AO9" t="n">
-        <v>15</v>
-      </c>
-      <c r="AP9" t="n">
-        <v>19</v>
-      </c>
       <c r="AQ9" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="AR9" t="n">
         <v>12</v>
       </c>
       <c r="AS9" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="AT9" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AU9" t="n">
         <v>3</v>
@@ -2079,13 +2146,13 @@
         <v>1</v>
       </c>
       <c r="AZ9" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BA9" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BB9" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BC9" t="n">
         <v>3</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>12-9-2007-08</t>
+          <t>2007-12-09</t>
         </is>
       </c>
     </row>
@@ -2117,97 +2184,97 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E10" t="n">
         <v>11</v>
       </c>
       <c r="F10" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G10" t="n">
-        <v>0.55</v>
+        <v>0.579</v>
       </c>
       <c r="H10" t="n">
         <v>48.5</v>
       </c>
       <c r="I10" t="n">
-        <v>41</v>
+        <v>40.8</v>
       </c>
       <c r="J10" t="n">
-        <v>90.59999999999999</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="K10" t="n">
-        <v>0.452</v>
+        <v>0.451</v>
       </c>
       <c r="L10" t="n">
-        <v>9.6</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="M10" t="n">
-        <v>27.5</v>
+        <v>27.2</v>
       </c>
       <c r="N10" t="n">
-        <v>0.349</v>
+        <v>0.356</v>
       </c>
       <c r="O10" t="n">
-        <v>18.9</v>
+        <v>19</v>
       </c>
       <c r="P10" t="n">
-        <v>26.5</v>
+        <v>26.7</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.715</v>
+        <v>0.712</v>
       </c>
       <c r="R10" t="n">
-        <v>12.7</v>
+        <v>12.5</v>
       </c>
       <c r="S10" t="n">
-        <v>30.5</v>
+        <v>30.4</v>
       </c>
       <c r="T10" t="n">
-        <v>43.2</v>
+        <v>42.9</v>
       </c>
       <c r="U10" t="n">
-        <v>22.9</v>
+        <v>22.8</v>
       </c>
       <c r="V10" t="n">
-        <v>13.4</v>
+        <v>13.2</v>
       </c>
       <c r="W10" t="n">
-        <v>9.1</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="X10" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="Y10" t="n">
-        <v>5.8</v>
+        <v>5.6</v>
       </c>
       <c r="Z10" t="n">
-        <v>23.3</v>
+        <v>23.2</v>
       </c>
       <c r="AA10" t="n">
         <v>22.7</v>
       </c>
       <c r="AB10" t="n">
-        <v>110.4</v>
+        <v>110.3</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.3</v>
+        <v>2.9</v>
       </c>
       <c r="AD10" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="AE10" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AF10" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="AG10" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AH10" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="AI10" t="n">
         <v>2</v>
@@ -2225,43 +2292,43 @@
         <v>1</v>
       </c>
       <c r="AN10" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="AO10" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AP10" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AQ10" t="n">
         <v>25</v>
       </c>
       <c r="AR10" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AS10" t="n">
         <v>17</v>
       </c>
       <c r="AT10" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AU10" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AV10" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AW10" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AX10" t="n">
         <v>20</v>
       </c>
       <c r="AY10" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="AZ10" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BA10" t="n">
         <v>11</v>
@@ -2270,7 +2337,7 @@
         <v>1</v>
       </c>
       <c r="BC10" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="BD10" t="n">
         <v>10</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>12-9-2007-08</t>
+          <t>2007-12-09</t>
         </is>
       </c>
     </row>
@@ -2299,28 +2366,28 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E11" t="n">
         <v>11</v>
       </c>
       <c r="F11" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G11" t="n">
-        <v>0.524</v>
+        <v>0.55</v>
       </c>
       <c r="H11" t="n">
         <v>48</v>
       </c>
       <c r="I11" t="n">
-        <v>36.2</v>
+        <v>36.7</v>
       </c>
       <c r="J11" t="n">
-        <v>81.8</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="K11" t="n">
-        <v>0.443</v>
+        <v>0.445</v>
       </c>
       <c r="L11" t="n">
         <v>6.1</v>
@@ -2329,58 +2396,58 @@
         <v>19.2</v>
       </c>
       <c r="N11" t="n">
-        <v>0.32</v>
+        <v>0.318</v>
       </c>
       <c r="O11" t="n">
         <v>16.6</v>
       </c>
       <c r="P11" t="n">
-        <v>22.8</v>
+        <v>22.7</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.73</v>
+        <v>0.731</v>
       </c>
       <c r="R11" t="n">
-        <v>12.3</v>
+        <v>12.6</v>
       </c>
       <c r="S11" t="n">
-        <v>31.8</v>
+        <v>32.1</v>
       </c>
       <c r="T11" t="n">
-        <v>44.1</v>
+        <v>44.6</v>
       </c>
       <c r="U11" t="n">
-        <v>20.7</v>
+        <v>21</v>
       </c>
       <c r="V11" t="n">
         <v>14.1</v>
       </c>
       <c r="W11" t="n">
-        <v>7.6</v>
+        <v>7.7</v>
       </c>
       <c r="X11" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="Y11" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="Z11" t="n">
-        <v>21.3</v>
+        <v>21.4</v>
       </c>
       <c r="AA11" t="n">
-        <v>20.4</v>
+        <v>20.5</v>
       </c>
       <c r="AB11" t="n">
-        <v>95.2</v>
+        <v>96</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.6</v>
+        <v>2.3</v>
       </c>
       <c r="AD11" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="AE11" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AF11" t="n">
         <v>12</v>
@@ -2389,13 +2456,13 @@
         <v>12</v>
       </c>
       <c r="AH11" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AI11" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="AJ11" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AK11" t="n">
         <v>19</v>
@@ -2404,10 +2471,10 @@
         <v>14</v>
       </c>
       <c r="AM11" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AN11" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AO11" t="n">
         <v>27</v>
@@ -2416,44 +2483,44 @@
         <v>23</v>
       </c>
       <c r="AQ11" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AR11" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AS11" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AT11" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="AU11" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="AV11" t="n">
         <v>7</v>
       </c>
       <c r="AW11" t="n">
+        <v>13</v>
+      </c>
+      <c r="AX11" t="n">
         <v>14</v>
       </c>
-      <c r="AX11" t="n">
+      <c r="AY11" t="n">
+        <v>11</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>14</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>22</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>18</v>
+      </c>
+      <c r="BC11" t="n">
         <v>12</v>
       </c>
-      <c r="AY11" t="n">
-        <v>13</v>
-      </c>
-      <c r="AZ11" t="n">
-        <v>13</v>
-      </c>
-      <c r="BA11" t="n">
-        <v>23</v>
-      </c>
-      <c r="BB11" t="n">
-        <v>20</v>
-      </c>
-      <c r="BC11" t="n">
-        <v>13</v>
-      </c>
       <c r="BD11" t="n">
         <v>10</v>
       </c>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>12-9-2007-08</t>
+          <t>2007-12-09</t>
         </is>
       </c>
     </row>
@@ -2559,19 +2626,19 @@
         <v>-1.1</v>
       </c>
       <c r="AD12" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="AE12" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AF12" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AG12" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AH12" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AI12" t="n">
         <v>7</v>
@@ -2589,28 +2656,28 @@
         <v>4</v>
       </c>
       <c r="AN12" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AO12" t="n">
         <v>12</v>
       </c>
       <c r="AP12" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AQ12" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AR12" t="n">
         <v>4</v>
       </c>
       <c r="AS12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AT12" t="n">
         <v>1</v>
       </c>
       <c r="AU12" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AV12" t="n">
         <v>23</v>
@@ -2619,10 +2686,10 @@
         <v>10</v>
       </c>
       <c r="AX12" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AY12" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AZ12" t="n">
         <v>30</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>12-9-2007-08</t>
+          <t>2007-12-09</t>
         </is>
       </c>
     </row>
@@ -2663,76 +2730,76 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E13" t="n">
         <v>7</v>
       </c>
       <c r="F13" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G13" t="n">
-        <v>0.368</v>
+        <v>0.389</v>
       </c>
       <c r="H13" t="n">
         <v>48</v>
       </c>
       <c r="I13" t="n">
-        <v>33.1</v>
+        <v>32.9</v>
       </c>
       <c r="J13" t="n">
         <v>78.7</v>
       </c>
       <c r="K13" t="n">
-        <v>0.42</v>
+        <v>0.418</v>
       </c>
       <c r="L13" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="M13" t="n">
-        <v>15.8</v>
+        <v>15.9</v>
       </c>
       <c r="N13" t="n">
-        <v>0.357</v>
+        <v>0.355</v>
       </c>
       <c r="O13" t="n">
-        <v>22.2</v>
+        <v>22.6</v>
       </c>
       <c r="P13" t="n">
-        <v>27.8</v>
+        <v>28.4</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.796</v>
+        <v>0.795</v>
       </c>
       <c r="R13" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="S13" t="n">
-        <v>32.7</v>
+        <v>32.9</v>
       </c>
       <c r="T13" t="n">
-        <v>42.2</v>
+        <v>42.5</v>
       </c>
       <c r="U13" t="n">
-        <v>20.7</v>
+        <v>20.1</v>
       </c>
       <c r="V13" t="n">
         <v>15.7</v>
       </c>
       <c r="W13" t="n">
-        <v>6.5</v>
+        <v>6.4</v>
       </c>
       <c r="X13" t="n">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="Y13" t="n">
         <v>5.2</v>
       </c>
       <c r="Z13" t="n">
-        <v>22</v>
+        <v>21.9</v>
       </c>
       <c r="AA13" t="n">
-        <v>21.9</v>
+        <v>22.2</v>
       </c>
       <c r="AB13" t="n">
         <v>94</v>
@@ -2741,19 +2808,19 @@
         <v>-4.8</v>
       </c>
       <c r="AD13" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="AE13" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AF13" t="n">
         <v>18</v>
       </c>
       <c r="AG13" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AH13" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AI13" t="n">
         <v>29</v>
@@ -2765,22 +2832,22 @@
         <v>29</v>
       </c>
       <c r="AL13" t="n">
+        <v>20</v>
+      </c>
+      <c r="AM13" t="n">
         <v>21</v>
       </c>
-      <c r="AM13" t="n">
-        <v>23</v>
-      </c>
       <c r="AN13" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AO13" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AP13" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AQ13" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AR13" t="n">
         <v>25</v>
@@ -2789,10 +2856,10 @@
         <v>8</v>
       </c>
       <c r="AT13" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AU13" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="AV13" t="n">
         <v>17</v>
@@ -2801,7 +2868,7 @@
         <v>25</v>
       </c>
       <c r="AX13" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AY13" t="n">
         <v>18</v>
@@ -2810,13 +2877,13 @@
         <v>17</v>
       </c>
       <c r="BA13" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BB13" t="n">
         <v>21</v>
       </c>
       <c r="BC13" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BD13" t="n">
         <v>10</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>12-9-2007-08</t>
+          <t>2007-12-09</t>
         </is>
       </c>
     </row>
@@ -2845,67 +2912,67 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E14" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F14" t="n">
         <v>8</v>
       </c>
       <c r="G14" t="n">
-        <v>0.6</v>
+        <v>0.579</v>
       </c>
       <c r="H14" t="n">
         <v>48</v>
       </c>
       <c r="I14" t="n">
-        <v>38.4</v>
+        <v>38.2</v>
       </c>
       <c r="J14" t="n">
         <v>81.3</v>
       </c>
       <c r="K14" t="n">
-        <v>0.472</v>
+        <v>0.469</v>
       </c>
       <c r="L14" t="n">
-        <v>7.3</v>
+        <v>7.2</v>
       </c>
       <c r="M14" t="n">
-        <v>20</v>
+        <v>20.1</v>
       </c>
       <c r="N14" t="n">
-        <v>0.363</v>
+        <v>0.359</v>
       </c>
       <c r="O14" t="n">
-        <v>23.1</v>
+        <v>22.8</v>
       </c>
       <c r="P14" t="n">
-        <v>30</v>
+        <v>29.5</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.771</v>
+        <v>0.772</v>
       </c>
       <c r="R14" t="n">
-        <v>10.7</v>
+        <v>10.9</v>
       </c>
       <c r="S14" t="n">
         <v>33.6</v>
       </c>
       <c r="T14" t="n">
-        <v>44.3</v>
+        <v>44.6</v>
       </c>
       <c r="U14" t="n">
-        <v>23.5</v>
+        <v>23.3</v>
       </c>
       <c r="V14" t="n">
         <v>16.6</v>
       </c>
       <c r="W14" t="n">
-        <v>8.9</v>
+        <v>9</v>
       </c>
       <c r="X14" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="Y14" t="n">
         <v>5.1</v>
@@ -2914,16 +2981,16 @@
         <v>22.4</v>
       </c>
       <c r="AA14" t="n">
-        <v>23.5</v>
+        <v>23.3</v>
       </c>
       <c r="AB14" t="n">
-        <v>107.2</v>
+        <v>106.3</v>
       </c>
       <c r="AC14" t="n">
-        <v>4.7</v>
+        <v>4.4</v>
       </c>
       <c r="AD14" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="AE14" t="n">
         <v>10</v>
@@ -2935,7 +3002,7 @@
         <v>10</v>
       </c>
       <c r="AH14" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AI14" t="n">
         <v>5</v>
@@ -2944,7 +3011,7 @@
         <v>13</v>
       </c>
       <c r="AK14" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AL14" t="n">
         <v>11</v>
@@ -2953,13 +3020,13 @@
         <v>7</v>
       </c>
       <c r="AN14" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AO14" t="n">
         <v>4</v>
       </c>
       <c r="AP14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AQ14" t="n">
         <v>8</v>
@@ -2968,34 +3035,34 @@
         <v>18</v>
       </c>
       <c r="AS14" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AT14" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AU14" t="n">
         <v>6</v>
       </c>
       <c r="AV14" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AW14" t="n">
         <v>5</v>
       </c>
       <c r="AX14" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="AY14" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AZ14" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="BA14" t="n">
+        <v>6</v>
+      </c>
+      <c r="BB14" t="n">
         <v>5</v>
-      </c>
-      <c r="BB14" t="n">
-        <v>3</v>
       </c>
       <c r="BC14" t="n">
         <v>8</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>12-9-2007-08</t>
+          <t>2007-12-09</t>
         </is>
       </c>
     </row>
@@ -3105,7 +3172,7 @@
         <v>-2</v>
       </c>
       <c r="AD15" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="AE15" t="n">
         <v>25</v>
@@ -3117,7 +3184,7 @@
         <v>27</v>
       </c>
       <c r="AH15" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AI15" t="n">
         <v>11</v>
@@ -3165,7 +3232,7 @@
         <v>30</v>
       </c>
       <c r="AX15" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AY15" t="n">
         <v>16</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>12-9-2007-08</t>
+          <t>2007-12-09</t>
         </is>
       </c>
     </row>
@@ -3209,64 +3276,64 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E16" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F16" t="n">
         <v>15</v>
       </c>
       <c r="G16" t="n">
-        <v>0.25</v>
+        <v>0.211</v>
       </c>
       <c r="H16" t="n">
         <v>48</v>
       </c>
       <c r="I16" t="n">
-        <v>35</v>
+        <v>34.8</v>
       </c>
       <c r="J16" t="n">
-        <v>76.7</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="K16" t="n">
-        <v>0.457</v>
+        <v>0.454</v>
       </c>
       <c r="L16" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="M16" t="n">
-        <v>14.1</v>
+        <v>14.5</v>
       </c>
       <c r="N16" t="n">
-        <v>0.349</v>
+        <v>0.345</v>
       </c>
       <c r="O16" t="n">
-        <v>17.1</v>
+        <v>17</v>
       </c>
       <c r="P16" t="n">
-        <v>25.5</v>
+        <v>25.4</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.672</v>
+        <v>0.67</v>
       </c>
       <c r="R16" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="S16" t="n">
-        <v>30.2</v>
+        <v>30.3</v>
       </c>
       <c r="T16" t="n">
-        <v>39.4</v>
+        <v>39.7</v>
       </c>
       <c r="U16" t="n">
-        <v>19.4</v>
+        <v>19.2</v>
       </c>
       <c r="V16" t="n">
-        <v>15</v>
+        <v>15.1</v>
       </c>
       <c r="W16" t="n">
-        <v>7.5</v>
+        <v>7.6</v>
       </c>
       <c r="X16" t="n">
         <v>5.2</v>
@@ -3275,31 +3342,31 @@
         <v>3.5</v>
       </c>
       <c r="Z16" t="n">
-        <v>20.6</v>
+        <v>20.7</v>
       </c>
       <c r="AA16" t="n">
-        <v>21.3</v>
+        <v>21.2</v>
       </c>
       <c r="AB16" t="n">
-        <v>92</v>
+        <v>91.59999999999999</v>
       </c>
       <c r="AC16" t="n">
-        <v>-4.9</v>
+        <v>-5.4</v>
       </c>
       <c r="AD16" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="AE16" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AF16" t="n">
         <v>28</v>
       </c>
       <c r="AG16" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AH16" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AI16" t="n">
         <v>24</v>
@@ -3308,19 +3375,19 @@
         <v>28</v>
       </c>
       <c r="AK16" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="AL16" t="n">
         <v>25</v>
       </c>
       <c r="AM16" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AN16" t="n">
         <v>18</v>
       </c>
       <c r="AO16" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AP16" t="n">
         <v>18</v>
@@ -3332,37 +3399,37 @@
         <v>26</v>
       </c>
       <c r="AS16" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AT16" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AU16" t="n">
         <v>25</v>
       </c>
       <c r="AV16" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AW16" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AX16" t="n">
         <v>9</v>
       </c>
       <c r="AY16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AZ16" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BA16" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="BB16" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="BC16" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="BD16" t="n">
         <v>10</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>12-9-2007-08</t>
+          <t>2007-12-09</t>
         </is>
       </c>
     </row>
@@ -3391,160 +3458,160 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E17" t="n">
         <v>8</v>
       </c>
       <c r="F17" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G17" t="n">
-        <v>0.421</v>
+        <v>0.444</v>
       </c>
       <c r="H17" t="n">
-        <v>48.3</v>
+        <v>48</v>
       </c>
       <c r="I17" t="n">
-        <v>36.5</v>
+        <v>36.3</v>
       </c>
       <c r="J17" t="n">
-        <v>80.5</v>
+        <v>79.90000000000001</v>
       </c>
       <c r="K17" t="n">
-        <v>0.454</v>
+        <v>0.455</v>
       </c>
       <c r="L17" t="n">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="M17" t="n">
-        <v>14.7</v>
+        <v>14.4</v>
       </c>
       <c r="N17" t="n">
-        <v>0.333</v>
+        <v>0.328</v>
       </c>
       <c r="O17" t="n">
-        <v>17.8</v>
+        <v>17.4</v>
       </c>
       <c r="P17" t="n">
-        <v>23.9</v>
+        <v>23.7</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.743</v>
+        <v>0.733</v>
       </c>
       <c r="R17" t="n">
-        <v>12.3</v>
+        <v>12.1</v>
       </c>
       <c r="S17" t="n">
-        <v>28.8</v>
+        <v>29.3</v>
       </c>
       <c r="T17" t="n">
-        <v>41.1</v>
+        <v>41.3</v>
       </c>
       <c r="U17" t="n">
-        <v>20.9</v>
+        <v>20.8</v>
       </c>
       <c r="V17" t="n">
         <v>15.2</v>
       </c>
       <c r="W17" t="n">
-        <v>6.5</v>
+        <v>6.3</v>
       </c>
       <c r="X17" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="Y17" t="n">
         <v>5.7</v>
       </c>
       <c r="Z17" t="n">
-        <v>21.5</v>
+        <v>21.3</v>
       </c>
       <c r="AA17" t="n">
-        <v>22.1</v>
+        <v>22</v>
       </c>
       <c r="AB17" t="n">
-        <v>95.7</v>
+        <v>94.8</v>
       </c>
       <c r="AC17" t="n">
         <v>-5.1</v>
       </c>
       <c r="AD17" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="AE17" t="n">
         <v>19</v>
       </c>
       <c r="AF17" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="AG17" t="n">
+        <v>18</v>
+      </c>
+      <c r="AH17" t="n">
         <v>19</v>
       </c>
-      <c r="AH17" t="n">
-        <v>15</v>
-      </c>
       <c r="AI17" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AJ17" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="AK17" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AL17" t="n">
         <v>26</v>
       </c>
       <c r="AM17" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AN17" t="n">
         <v>24</v>
       </c>
       <c r="AO17" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AP17" t="n">
         <v>22</v>
       </c>
       <c r="AQ17" t="n">
+        <v>20</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>11</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>23</v>
+      </c>
+      <c r="AT17" t="n">
         <v>19</v>
       </c>
-      <c r="AR17" t="n">
-        <v>9</v>
-      </c>
-      <c r="AS17" t="n">
-        <v>29</v>
-      </c>
-      <c r="AT17" t="n">
-        <v>22</v>
-      </c>
       <c r="AU17" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AV17" t="n">
         <v>12</v>
       </c>
       <c r="AW17" t="n">
+        <v>27</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>8</v>
+      </c>
+      <c r="AY17" t="n">
         <v>25</v>
       </c>
-      <c r="AX17" t="n">
+      <c r="AZ17" t="n">
+        <v>13</v>
+      </c>
+      <c r="BA17" t="n">
         <v>14</v>
       </c>
-      <c r="AY17" t="n">
-        <v>24</v>
-      </c>
-      <c r="AZ17" t="n">
-        <v>14</v>
-      </c>
-      <c r="BA17" t="n">
-        <v>13</v>
-      </c>
       <c r="BB17" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="BC17" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="BD17" t="n">
         <v>10</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>12-9-2007-08</t>
+          <t>2007-12-09</t>
         </is>
       </c>
     </row>
@@ -3651,7 +3718,7 @@
         <v>-8.300000000000001</v>
       </c>
       <c r="AD18" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="AE18" t="n">
         <v>30</v>
@@ -3663,13 +3730,13 @@
         <v>30</v>
       </c>
       <c r="AH18" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AI18" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AJ18" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AK18" t="n">
         <v>20</v>
@@ -3681,7 +3748,7 @@
         <v>18</v>
       </c>
       <c r="AN18" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AO18" t="n">
         <v>30</v>
@@ -3714,7 +3781,7 @@
         <v>22</v>
       </c>
       <c r="AY18" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AZ18" t="n">
         <v>29</v>
@@ -3723,7 +3790,7 @@
         <v>29</v>
       </c>
       <c r="BB18" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BC18" t="n">
         <v>29</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>12-9-2007-08</t>
+          <t>2007-12-09</t>
         </is>
       </c>
     </row>
@@ -3755,88 +3822,88 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E19" t="n">
         <v>9</v>
       </c>
       <c r="F19" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G19" t="n">
-        <v>0.429</v>
+        <v>0.45</v>
       </c>
       <c r="H19" t="n">
         <v>48.5</v>
       </c>
       <c r="I19" t="n">
-        <v>31.8</v>
+        <v>31.7</v>
       </c>
       <c r="J19" t="n">
-        <v>74.59999999999999</v>
+        <v>74.8</v>
       </c>
       <c r="K19" t="n">
-        <v>0.426</v>
+        <v>0.423</v>
       </c>
       <c r="L19" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="M19" t="n">
-        <v>17.6</v>
+        <v>17.4</v>
       </c>
       <c r="N19" t="n">
-        <v>0.324</v>
+        <v>0.322</v>
       </c>
       <c r="O19" t="n">
-        <v>21.2</v>
+        <v>21.7</v>
       </c>
       <c r="P19" t="n">
-        <v>28.4</v>
+        <v>29</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.747</v>
+        <v>0.748</v>
       </c>
       <c r="R19" t="n">
-        <v>10.2</v>
+        <v>10.4</v>
       </c>
       <c r="S19" t="n">
         <v>30.2</v>
       </c>
       <c r="T19" t="n">
-        <v>40.4</v>
+        <v>40.6</v>
       </c>
       <c r="U19" t="n">
-        <v>22.3</v>
+        <v>22.4</v>
       </c>
       <c r="V19" t="n">
-        <v>16.6</v>
+        <v>16.5</v>
       </c>
       <c r="W19" t="n">
-        <v>6.3</v>
+        <v>6.4</v>
       </c>
       <c r="X19" t="n">
         <v>4.8</v>
       </c>
       <c r="Y19" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="Z19" t="n">
         <v>24</v>
       </c>
       <c r="AA19" t="n">
-        <v>23.3</v>
+        <v>23.9</v>
       </c>
       <c r="AB19" t="n">
-        <v>90.5</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="AC19" t="n">
-        <v>-6.2</v>
+        <v>-5.8</v>
       </c>
       <c r="AD19" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="AE19" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AF19" t="n">
         <v>18</v>
@@ -3845,7 +3912,7 @@
         <v>17</v>
       </c>
       <c r="AH19" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AI19" t="n">
         <v>30</v>
@@ -3857,7 +3924,7 @@
         <v>28</v>
       </c>
       <c r="AL19" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AM19" t="n">
         <v>14</v>
@@ -3866,43 +3933,43 @@
         <v>25</v>
       </c>
       <c r="AO19" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AP19" t="n">
         <v>6</v>
       </c>
       <c r="AQ19" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AR19" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AS19" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AT19" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AU19" t="n">
         <v>11</v>
       </c>
       <c r="AV19" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AW19" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AX19" t="n">
         <v>19</v>
       </c>
       <c r="AY19" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="AZ19" t="n">
         <v>27</v>
       </c>
       <c r="BA19" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BB19" t="n">
         <v>29</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>12-9-2007-08</t>
+          <t>2007-12-09</t>
         </is>
       </c>
     </row>
@@ -3937,85 +4004,85 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E20" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F20" t="n">
         <v>7</v>
       </c>
       <c r="G20" t="n">
-        <v>0.667</v>
+        <v>0.65</v>
       </c>
       <c r="H20" t="n">
-        <v>48.7</v>
+        <v>48.8</v>
       </c>
       <c r="I20" t="n">
         <v>36.3</v>
       </c>
       <c r="J20" t="n">
-        <v>82.3</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="K20" t="n">
-        <v>0.441</v>
+        <v>0.44</v>
       </c>
       <c r="L20" t="n">
-        <v>7.3</v>
+        <v>7.6</v>
       </c>
       <c r="M20" t="n">
-        <v>19.3</v>
+        <v>19.8</v>
       </c>
       <c r="N20" t="n">
-        <v>0.377</v>
+        <v>0.382</v>
       </c>
       <c r="O20" t="n">
-        <v>16.7</v>
+        <v>16.8</v>
       </c>
       <c r="P20" t="n">
-        <v>21.3</v>
+        <v>21</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.785</v>
+        <v>0.8</v>
       </c>
       <c r="R20" t="n">
-        <v>11.2</v>
+        <v>11.3</v>
       </c>
       <c r="S20" t="n">
-        <v>31.5</v>
+        <v>31.4</v>
       </c>
       <c r="T20" t="n">
         <v>42.7</v>
       </c>
       <c r="U20" t="n">
-        <v>20.1</v>
+        <v>20.2</v>
       </c>
       <c r="V20" t="n">
-        <v>13.2</v>
+        <v>13.3</v>
       </c>
       <c r="W20" t="n">
-        <v>7.6</v>
+        <v>7.7</v>
       </c>
       <c r="X20" t="n">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="Y20" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="Z20" t="n">
-        <v>19.8</v>
+        <v>19.9</v>
       </c>
       <c r="AA20" t="n">
-        <v>19.6</v>
+        <v>19.7</v>
       </c>
       <c r="AB20" t="n">
-        <v>96.59999999999999</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="AC20" t="n">
         <v>2.5</v>
       </c>
       <c r="AD20" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="AE20" t="n">
         <v>5</v>
@@ -4030,7 +4097,7 @@
         <v>1</v>
       </c>
       <c r="AI20" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AJ20" t="n">
         <v>10</v>
@@ -4039,22 +4106,22 @@
         <v>21</v>
       </c>
       <c r="AL20" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AM20" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AN20" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AO20" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AP20" t="n">
         <v>28</v>
       </c>
       <c r="AQ20" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AR20" t="n">
         <v>16</v>
@@ -4066,22 +4133,22 @@
         <v>12</v>
       </c>
       <c r="AU20" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AV20" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AW20" t="n">
         <v>13</v>
       </c>
       <c r="AX20" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AY20" t="n">
         <v>5</v>
       </c>
       <c r="AZ20" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="BA20" t="n">
         <v>27</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>12-9-2007-08</t>
+          <t>2007-12-09</t>
         </is>
       </c>
     </row>
@@ -4197,7 +4264,7 @@
         <v>-8.9</v>
       </c>
       <c r="AD21" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="AE21" t="n">
         <v>25</v>
@@ -4215,7 +4282,7 @@
         <v>25</v>
       </c>
       <c r="AJ21" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AK21" t="n">
         <v>27</v>
@@ -4227,10 +4294,10 @@
         <v>20</v>
       </c>
       <c r="AN21" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AO21" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AP21" t="n">
         <v>10</v>
@@ -4239,13 +4306,13 @@
         <v>28</v>
       </c>
       <c r="AR21" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AS21" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AT21" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AU21" t="n">
         <v>29</v>
@@ -4263,13 +4330,13 @@
         <v>28</v>
       </c>
       <c r="AZ21" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BA21" t="n">
         <v>12</v>
       </c>
       <c r="BB21" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BC21" t="n">
         <v>30</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>12-9-2007-08</t>
+          <t>2007-12-09</t>
         </is>
       </c>
     </row>
@@ -4391,10 +4458,10 @@
         <v>3</v>
       </c>
       <c r="AH22" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AI22" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AJ22" t="n">
         <v>19</v>
@@ -4409,10 +4476,10 @@
         <v>2</v>
       </c>
       <c r="AN22" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AO22" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AP22" t="n">
         <v>5</v>
@@ -4427,7 +4494,7 @@
         <v>1</v>
       </c>
       <c r="AT22" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AU22" t="n">
         <v>12</v>
@@ -4439,13 +4506,13 @@
         <v>24</v>
       </c>
       <c r="AX22" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AY22" t="n">
         <v>8</v>
       </c>
       <c r="AZ22" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BA22" t="n">
         <v>3</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>12-9-2007-08</t>
+          <t>2007-12-09</t>
         </is>
       </c>
     </row>
@@ -4561,10 +4628,10 @@
         <v>-1.2</v>
       </c>
       <c r="AD23" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="AE23" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AF23" t="n">
         <v>25</v>
@@ -4573,10 +4640,10 @@
         <v>24</v>
       </c>
       <c r="AH23" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AI23" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AJ23" t="n">
         <v>20</v>
@@ -4594,7 +4661,7 @@
         <v>28</v>
       </c>
       <c r="AO23" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AP23" t="n">
         <v>21</v>
@@ -4609,22 +4676,22 @@
         <v>20</v>
       </c>
       <c r="AT23" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AU23" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AV23" t="n">
         <v>20</v>
       </c>
       <c r="AW23" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AX23" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AY23" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AZ23" t="n">
         <v>12</v>
@@ -4633,7 +4700,7 @@
         <v>24</v>
       </c>
       <c r="BB23" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BC23" t="n">
         <v>16</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>12-9-2007-08</t>
+          <t>2007-12-09</t>
         </is>
       </c>
     </row>
@@ -4755,13 +4822,13 @@
         <v>3</v>
       </c>
       <c r="AH24" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AI24" t="n">
         <v>1</v>
       </c>
       <c r="AJ24" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AK24" t="n">
         <v>2</v>
@@ -4776,13 +4843,13 @@
         <v>8</v>
       </c>
       <c r="AO24" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AP24" t="n">
         <v>27</v>
       </c>
       <c r="AQ24" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AR24" t="n">
         <v>30</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>12-9-2007-08</t>
+          <t>2007-12-09</t>
         </is>
       </c>
     </row>
@@ -4847,160 +4914,160 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E25" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F25" t="n">
         <v>12</v>
       </c>
       <c r="G25" t="n">
-        <v>0.4</v>
+        <v>0.368</v>
       </c>
       <c r="H25" t="n">
-        <v>48.3</v>
+        <v>48</v>
       </c>
       <c r="I25" t="n">
-        <v>35.7</v>
+        <v>35.5</v>
       </c>
       <c r="J25" t="n">
-        <v>77.40000000000001</v>
+        <v>77.7</v>
       </c>
       <c r="K25" t="n">
-        <v>0.462</v>
+        <v>0.457</v>
       </c>
       <c r="L25" t="n">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="M25" t="n">
-        <v>15.8</v>
+        <v>15.7</v>
       </c>
       <c r="N25" t="n">
-        <v>0.38</v>
+        <v>0.372</v>
       </c>
       <c r="O25" t="n">
-        <v>16.3</v>
+        <v>15.7</v>
       </c>
       <c r="P25" t="n">
-        <v>22.1</v>
+        <v>21.6</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.739</v>
+        <v>0.727</v>
       </c>
       <c r="R25" t="n">
-        <v>9.6</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="S25" t="n">
-        <v>29.2</v>
+        <v>29.3</v>
       </c>
       <c r="T25" t="n">
-        <v>38.8</v>
+        <v>39</v>
       </c>
       <c r="U25" t="n">
-        <v>20.8</v>
+        <v>20.6</v>
       </c>
       <c r="V25" t="n">
-        <v>15.2</v>
+        <v>15</v>
       </c>
       <c r="W25" t="n">
-        <v>5.9</v>
+        <v>5.7</v>
       </c>
       <c r="X25" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="Y25" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="Z25" t="n">
-        <v>20.6</v>
+        <v>20.4</v>
       </c>
       <c r="AA25" t="n">
-        <v>21.2</v>
+        <v>21</v>
       </c>
       <c r="AB25" t="n">
-        <v>93.7</v>
+        <v>92.5</v>
       </c>
       <c r="AC25" t="n">
-        <v>-4.8</v>
+        <v>-5.2</v>
       </c>
       <c r="AD25" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="AE25" t="n">
+        <v>20</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>21</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>22</v>
+      </c>
+      <c r="AH25" t="n">
         <v>19</v>
       </c>
-      <c r="AF25" t="n">
-        <v>18</v>
-      </c>
-      <c r="AG25" t="n">
-        <v>20</v>
-      </c>
-      <c r="AH25" t="n">
-        <v>17</v>
-      </c>
       <c r="AI25" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AJ25" t="n">
         <v>27</v>
       </c>
       <c r="AK25" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AL25" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AM25" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AN25" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AO25" t="n">
         <v>28</v>
       </c>
       <c r="AP25" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AQ25" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AR25" t="n">
         <v>24</v>
       </c>
       <c r="AS25" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="AT25" t="n">
         <v>30</v>
       </c>
       <c r="AU25" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AV25" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AW25" t="n">
         <v>28</v>
       </c>
       <c r="AX25" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AY25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AZ25" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="BA25" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BB25" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="BC25" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="BD25" t="n">
         <v>10</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>12-9-2007-08</t>
+          <t>2007-12-09</t>
         </is>
       </c>
     </row>
@@ -5107,16 +5174,16 @@
         <v>-3.4</v>
       </c>
       <c r="AD26" t="n">
+        <v>16</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>20</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>21</v>
+      </c>
+      <c r="AG26" t="n">
         <v>22</v>
-      </c>
-      <c r="AE26" t="n">
-        <v>21</v>
-      </c>
-      <c r="AF26" t="n">
-        <v>18</v>
-      </c>
-      <c r="AG26" t="n">
-        <v>21</v>
       </c>
       <c r="AH26" t="n">
         <v>2</v>
@@ -5137,13 +5204,13 @@
         <v>24</v>
       </c>
       <c r="AN26" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AO26" t="n">
         <v>2</v>
       </c>
       <c r="AP26" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AQ26" t="n">
         <v>3</v>
@@ -5152,7 +5219,7 @@
         <v>22</v>
       </c>
       <c r="AS26" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AT26" t="n">
         <v>29</v>
@@ -5164,7 +5231,7 @@
         <v>16</v>
       </c>
       <c r="AW26" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AX26" t="n">
         <v>29</v>
@@ -5179,7 +5246,7 @@
         <v>1</v>
       </c>
       <c r="BB26" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BC26" t="n">
         <v>19</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>12-9-2007-08</t>
+          <t>2007-12-09</t>
         </is>
       </c>
     </row>
@@ -5289,7 +5356,7 @@
         <v>9</v>
       </c>
       <c r="AD27" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="AE27" t="n">
         <v>1</v>
@@ -5301,7 +5368,7 @@
         <v>2</v>
       </c>
       <c r="AH27" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AI27" t="n">
         <v>6</v>
@@ -5313,7 +5380,7 @@
         <v>4</v>
       </c>
       <c r="AL27" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AM27" t="n">
         <v>6</v>
@@ -5325,7 +5392,7 @@
         <v>23</v>
       </c>
       <c r="AP27" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AQ27" t="n">
         <v>9</v>
@@ -5337,7 +5404,7 @@
         <v>15</v>
       </c>
       <c r="AT27" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AU27" t="n">
         <v>10</v>
@@ -5349,7 +5416,7 @@
         <v>21</v>
       </c>
       <c r="AX27" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AY27" t="n">
         <v>10</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>12-9-2007-08</t>
+          <t>2007-12-09</t>
         </is>
       </c>
     </row>
@@ -5393,106 +5460,106 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E28" t="n">
         <v>5</v>
       </c>
       <c r="F28" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G28" t="n">
-        <v>0.238</v>
+        <v>0.25</v>
       </c>
       <c r="H28" t="n">
         <v>48.5</v>
       </c>
       <c r="I28" t="n">
-        <v>37</v>
+        <v>37.2</v>
       </c>
       <c r="J28" t="n">
-        <v>85.8</v>
+        <v>85.59999999999999</v>
       </c>
       <c r="K28" t="n">
-        <v>0.431</v>
+        <v>0.434</v>
       </c>
       <c r="L28" t="n">
         <v>4.7</v>
       </c>
       <c r="M28" t="n">
-        <v>13.1</v>
+        <v>13.3</v>
       </c>
       <c r="N28" t="n">
         <v>0.355</v>
       </c>
       <c r="O28" t="n">
-        <v>19.7</v>
+        <v>19.9</v>
       </c>
       <c r="P28" t="n">
-        <v>25.6</v>
+        <v>25.9</v>
       </c>
       <c r="Q28" t="n">
-        <v>0.77</v>
+        <v>0.768</v>
       </c>
       <c r="R28" t="n">
-        <v>11.8</v>
+        <v>11.5</v>
       </c>
       <c r="S28" t="n">
-        <v>34.1</v>
+        <v>34</v>
       </c>
       <c r="T28" t="n">
-        <v>45.9</v>
+        <v>45.4</v>
       </c>
       <c r="U28" t="n">
         <v>20</v>
       </c>
       <c r="V28" t="n">
-        <v>17.3</v>
+        <v>17.4</v>
       </c>
       <c r="W28" t="n">
-        <v>7.1</v>
+        <v>7.3</v>
       </c>
       <c r="X28" t="n">
         <v>5.2</v>
       </c>
       <c r="Y28" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="Z28" t="n">
-        <v>23.1</v>
+        <v>23.4</v>
       </c>
       <c r="AA28" t="n">
-        <v>21.1</v>
+        <v>21.3</v>
       </c>
       <c r="AB28" t="n">
-        <v>98.40000000000001</v>
+        <v>98.90000000000001</v>
       </c>
       <c r="AC28" t="n">
-        <v>-7.1</v>
+        <v>-7.3</v>
       </c>
       <c r="AD28" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="AE28" t="n">
         <v>28</v>
       </c>
       <c r="AF28" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="AG28" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AH28" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AI28" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AJ28" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AK28" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AL28" t="n">
         <v>27</v>
@@ -5501,16 +5568,16 @@
         <v>29</v>
       </c>
       <c r="AN28" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AO28" t="n">
         <v>14</v>
       </c>
       <c r="AP28" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AQ28" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AR28" t="n">
         <v>15</v>
@@ -5522,25 +5589,25 @@
         <v>2</v>
       </c>
       <c r="AU28" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AV28" t="n">
         <v>30</v>
       </c>
       <c r="AW28" t="n">
+        <v>17</v>
+      </c>
+      <c r="AX28" t="n">
+        <v>10</v>
+      </c>
+      <c r="AY28" t="n">
         <v>19</v>
       </c>
-      <c r="AX28" t="n">
-        <v>8</v>
-      </c>
-      <c r="AY28" t="n">
-        <v>20</v>
-      </c>
       <c r="AZ28" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="BA28" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="BB28" t="n">
         <v>16</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>12-9-2007-08</t>
+          <t>2007-12-09</t>
         </is>
       </c>
     </row>
@@ -5575,112 +5642,112 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E29" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F29" t="n">
         <v>10</v>
       </c>
       <c r="G29" t="n">
-        <v>0.524</v>
+        <v>0.5</v>
       </c>
       <c r="H29" t="n">
-        <v>48.2</v>
+        <v>48.3</v>
       </c>
       <c r="I29" t="n">
-        <v>37.8</v>
+        <v>37.9</v>
       </c>
       <c r="J29" t="n">
-        <v>83.40000000000001</v>
+        <v>83.3</v>
       </c>
       <c r="K29" t="n">
-        <v>0.453</v>
+        <v>0.454</v>
       </c>
       <c r="L29" t="n">
-        <v>8.300000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="M29" t="n">
-        <v>19</v>
+        <v>19.6</v>
       </c>
       <c r="N29" t="n">
-        <v>0.435</v>
+        <v>0.437</v>
       </c>
       <c r="O29" t="n">
-        <v>15</v>
+        <v>14.9</v>
       </c>
       <c r="P29" t="n">
-        <v>18.1</v>
+        <v>17.9</v>
       </c>
       <c r="Q29" t="n">
-        <v>0.829</v>
+        <v>0.832</v>
       </c>
       <c r="R29" t="n">
-        <v>10.5</v>
+        <v>10.1</v>
       </c>
       <c r="S29" t="n">
         <v>30.5</v>
       </c>
       <c r="T29" t="n">
-        <v>41</v>
+        <v>40.6</v>
       </c>
       <c r="U29" t="n">
         <v>23.1</v>
       </c>
       <c r="V29" t="n">
-        <v>12.5</v>
+        <v>12.7</v>
       </c>
       <c r="W29" t="n">
         <v>7</v>
       </c>
       <c r="X29" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="Y29" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="Z29" t="n">
-        <v>20.9</v>
+        <v>21</v>
       </c>
       <c r="AA29" t="n">
-        <v>17.6</v>
+        <v>17.5</v>
       </c>
       <c r="AB29" t="n">
-        <v>98.90000000000001</v>
+        <v>99.2</v>
       </c>
       <c r="AC29" t="n">
-        <v>2.8</v>
+        <v>2.3</v>
       </c>
       <c r="AD29" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="AE29" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AF29" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AG29" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AH29" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="AI29" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AJ29" t="n">
         <v>7</v>
       </c>
       <c r="AK29" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AL29" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AM29" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AN29" t="n">
         <v>1</v>
@@ -5695,13 +5762,13 @@
         <v>2</v>
       </c>
       <c r="AR29" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AS29" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AT29" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AU29" t="n">
         <v>7</v>
@@ -5713,7 +5780,7 @@
         <v>20</v>
       </c>
       <c r="AX29" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AY29" t="n">
         <v>14</v>
@@ -5728,7 +5795,7 @@
         <v>15</v>
       </c>
       <c r="BC29" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="BD29" t="n">
         <v>10</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>12-9-2007-08</t>
+          <t>2007-12-09</t>
         </is>
       </c>
     </row>
@@ -5838,7 +5905,7 @@
         <v>1</v>
       </c>
       <c r="AE30" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AF30" t="n">
         <v>7</v>
@@ -5847,13 +5914,13 @@
         <v>7</v>
       </c>
       <c r="AH30" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AI30" t="n">
         <v>3</v>
       </c>
       <c r="AJ30" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AK30" t="n">
         <v>1</v>
@@ -5865,10 +5932,10 @@
         <v>30</v>
       </c>
       <c r="AN30" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AO30" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AP30" t="n">
         <v>4</v>
@@ -5877,10 +5944,10 @@
         <v>14</v>
       </c>
       <c r="AR30" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AS30" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AT30" t="n">
         <v>21</v>
@@ -5892,13 +5959,13 @@
         <v>24</v>
       </c>
       <c r="AW30" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AX30" t="n">
         <v>25</v>
       </c>
       <c r="AY30" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AZ30" t="n">
         <v>28</v>
@@ -5907,7 +5974,7 @@
         <v>3</v>
       </c>
       <c r="BB30" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BC30" t="n">
         <v>4</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>12-9-2007-08</t>
+          <t>2007-12-09</t>
         </is>
       </c>
     </row>
@@ -5939,127 +6006,127 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E31" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F31" t="n">
         <v>10</v>
       </c>
       <c r="G31" t="n">
-        <v>0.5</v>
+        <v>0.474</v>
       </c>
       <c r="H31" t="n">
         <v>48.5</v>
       </c>
       <c r="I31" t="n">
-        <v>37.7</v>
+        <v>37.9</v>
       </c>
       <c r="J31" t="n">
-        <v>82.8</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="K31" t="n">
-        <v>0.455</v>
+        <v>0.457</v>
       </c>
       <c r="L31" t="n">
         <v>5.9</v>
       </c>
       <c r="M31" t="n">
-        <v>17.4</v>
+        <v>17.3</v>
       </c>
       <c r="N31" t="n">
-        <v>0.336</v>
+        <v>0.345</v>
       </c>
       <c r="O31" t="n">
-        <v>20.8</v>
+        <v>20.1</v>
       </c>
       <c r="P31" t="n">
-        <v>26.3</v>
+        <v>25.8</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.789</v>
+        <v>0.778</v>
       </c>
       <c r="R31" t="n">
         <v>12.5</v>
       </c>
       <c r="S31" t="n">
-        <v>30.9</v>
+        <v>31.1</v>
       </c>
       <c r="T31" t="n">
-        <v>43.4</v>
+        <v>43.6</v>
       </c>
       <c r="U31" t="n">
-        <v>20</v>
+        <v>20.2</v>
       </c>
       <c r="V31" t="n">
-        <v>14.5</v>
+        <v>14.7</v>
       </c>
       <c r="W31" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="X31" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="Y31" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="Z31" t="n">
-        <v>19.8</v>
+        <v>20.2</v>
       </c>
       <c r="AA31" t="n">
-        <v>21.5</v>
+        <v>21.3</v>
       </c>
       <c r="AB31" t="n">
-        <v>101.9</v>
+        <v>101.8</v>
       </c>
       <c r="AC31" t="n">
-        <v>0.7</v>
+        <v>-0.1</v>
       </c>
       <c r="AD31" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="AE31" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AF31" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AG31" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AH31" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="AI31" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AJ31" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AK31" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AL31" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AM31" t="n">
         <v>16</v>
       </c>
       <c r="AN31" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="AO31" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AP31" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="AQ31" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AR31" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AS31" t="n">
         <v>13</v>
@@ -6068,25 +6135,25 @@
         <v>8</v>
       </c>
       <c r="AU31" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="AV31" t="n">
         <v>9</v>
       </c>
       <c r="AW31" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AX31" t="n">
+        <v>6</v>
+      </c>
+      <c r="AY31" t="n">
         <v>7</v>
       </c>
-      <c r="AY31" t="n">
-        <v>9</v>
-      </c>
       <c r="AZ31" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="BA31" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BB31" t="n">
         <v>10</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>12-9-2007-08</t>
+          <t>2007-12-09</t>
         </is>
       </c>
     </row>
